--- a/templates/ERC000026/metadata_template_ERC000026.xlsx
+++ b/templates/ERC000026/metadata_template_ERC000026.xlsx
@@ -19,11 +19,11 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="gender">'cv_sample'!$I$1:$I$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="sampletype">'cv_sample'!$L$1:$L$16</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="308">
   <si>
     <t>alias</t>
   </si>
@@ -448,6 +448,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -538,6 +541,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -943,7 +949,7 @@
     <t>urine</t>
   </si>
   <si>
-    <t>sample_type</t>
+    <t>sample type</t>
   </si>
   <si>
     <t>donor_id</t>
@@ -1476,10 +1482,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -1520,10 +1526,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -1567,7 +1573,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -1584,7 +1590,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -1601,7 +1607,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -1618,7 +1624,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -1635,7 +1641,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -1652,7 +1658,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -1669,7 +1675,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -1686,7 +1692,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -1703,7 +1709,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -1717,7 +1723,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -1731,7 +1737,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -1745,7 +1751,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -1759,7 +1765,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -1773,7 +1779,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -1787,7 +1793,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -1801,7 +1807,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -1815,7 +1821,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -1825,8 +1831,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -1837,7 +1846,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -1848,7 +1857,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -1859,7 +1868,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -1870,7 +1879,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -1881,7 +1890,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -1892,7 +1901,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -1903,7 +1912,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -1914,7 +1923,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -1925,7 +1934,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -1936,7 +1945,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -1947,7 +1956,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -1958,7 +1967,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -1969,7 +1978,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -1977,7 +1986,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -1985,7 +1994,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -1993,7 +2002,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2001,7 +2010,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2009,7 +2018,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2017,7 +2026,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2025,7 +2034,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2033,7 +2042,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2041,7 +2050,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2049,236 +2058,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2300,27 +2314,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2340,122 +2354,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2479,78 +2493,78 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -2573,91 +2587,91 @@
   <sheetData>
     <row r="1" spans="9:12">
       <c r="I1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="9:12">
       <c r="I2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="9:12">
       <c r="I3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="9:12">
       <c r="L4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="9:12">
       <c r="L5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="9:12">
       <c r="L6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="9:12">
       <c r="L7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="9:12">
       <c r="L8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="9:12">
       <c r="L9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="9:12">
       <c r="L10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="9:12">
       <c r="L11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="9:12">
       <c r="L12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="9:12">
       <c r="L13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="9:12">
       <c r="L14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="9:12">
       <c r="L15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="9:12">
       <c r="L16" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000026/metadata_template_ERC000026.xlsx
+++ b/templates/ERC000026/metadata_template_ERC000026.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="gender">'cv_sample'!$G$1:$G$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="gender">'cv_sample'!$H$1:$H$3</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="sampletype">'cv_sample'!$J$1:$J$16</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="sampletype">'cv_sample'!$K$1:$K$16</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="306">
   <si>
     <t>alias</t>
   </si>
@@ -448,6 +448,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -538,6 +541,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -838,6 +844,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -931,7 +943,7 @@
     <t>urine</t>
   </si>
   <si>
-    <t>sample_type</t>
+    <t>sample type</t>
   </si>
   <si>
     <t>donor_id</t>
@@ -1464,10 +1476,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -1508,10 +1520,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -1538,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -1555,7 +1567,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -1572,7 +1584,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -1589,7 +1601,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -1606,7 +1618,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -1623,7 +1635,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -1640,7 +1652,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -1657,7 +1669,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -1674,7 +1686,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -1691,7 +1703,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -1705,7 +1717,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -1719,7 +1731,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -1733,7 +1745,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -1747,7 +1759,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -1761,7 +1773,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -1775,7 +1787,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -1789,7 +1801,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -1803,7 +1815,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -1813,8 +1825,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -1825,7 +1840,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -1836,7 +1851,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -1847,7 +1862,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -1858,7 +1873,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -1869,7 +1884,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -1880,7 +1895,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -1891,7 +1906,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -1902,7 +1917,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -1913,7 +1928,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -1924,7 +1939,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -1935,7 +1950,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -1946,7 +1961,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -1957,7 +1972,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -1965,7 +1980,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -1973,7 +1988,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -1981,7 +1996,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -1989,7 +2004,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -1997,7 +2012,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2005,7 +2020,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2013,7 +2028,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2021,7 +2036,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2029,7 +2044,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2037,236 +2052,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2288,27 +2308,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2328,122 +2348,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2453,13 +2473,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2467,74 +2487,80 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="150" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="150" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>301</v>
+        <v>286</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>gender</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>sampletype</formula1>
     </dataValidation>
   </dataValidations>
@@ -2544,96 +2570,96 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:J16"/>
+  <dimension ref="H1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="7:10">
-      <c r="G1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="2" spans="7:10">
-      <c r="G2" t="s">
-        <v>275</v>
-      </c>
-      <c r="J2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="7:10">
-      <c r="G3" t="s">
-        <v>276</v>
-      </c>
-      <c r="J3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="7:10">
-      <c r="J4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="5" spans="7:10">
-      <c r="J5" t="s">
+    <row r="1" spans="8:11">
+      <c r="H1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="6" spans="7:10">
-      <c r="J6" t="s">
+    <row r="2" spans="8:11">
+      <c r="H2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="7:10">
-      <c r="J7" t="s">
+    <row r="3" spans="8:11">
+      <c r="H3" t="s">
+        <v>280</v>
+      </c>
+      <c r="K3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="8" spans="7:10">
-      <c r="J8" t="s">
+    <row r="4" spans="8:11">
+      <c r="K4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="9" spans="7:10">
-      <c r="J9" t="s">
+    <row r="5" spans="8:11">
+      <c r="K5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="7:10">
-      <c r="J10" t="s">
+    <row r="6" spans="8:11">
+      <c r="K6" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="7:10">
-      <c r="J11" t="s">
+    <row r="7" spans="8:11">
+      <c r="K7" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="7:10">
-      <c r="J12" t="s">
+    <row r="8" spans="8:11">
+      <c r="K8" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="7:10">
-      <c r="J13" t="s">
+    <row r="9" spans="8:11">
+      <c r="K9" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="7:10">
-      <c r="J14" t="s">
+    <row r="10" spans="8:11">
+      <c r="K10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="7:10">
-      <c r="J15" t="s">
+    <row r="11" spans="8:11">
+      <c r="K11" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="16" spans="7:10">
-      <c r="J16" t="s">
+    <row r="12" spans="8:11">
+      <c r="K12" t="s">
         <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11">
+      <c r="K13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="8:11">
+      <c r="K14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11">
+      <c r="K15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="8:11">
+      <c r="K16" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000026/metadata_template_ERC000026.xlsx
+++ b/templates/ERC000026/metadata_template_ERC000026.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="gender">'cv_sample'!$H$1:$H$3</definedName>
+    <definedName name="gender">'cv_sample'!$I$1:$I$3</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="sampletype">'cv_sample'!$K$1:$K$16</definedName>
+    <definedName name="sampletype">'cv_sample'!$L$1:$L$16</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="308">
   <si>
     <t>alias</t>
   </si>
@@ -848,6 +848,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -2473,13 +2479,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2502,7 +2508,7 @@
         <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>283</v>
@@ -2511,13 +2517,16 @@
         <v>285</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="150" customHeight="1">
+        <v>305</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -2540,7 +2549,7 @@
         <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>284</v>
@@ -2549,18 +2558,21 @@
         <v>286</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>305</v>
+        <v>288</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>gender</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
       <formula1>sampletype</formula1>
     </dataValidation>
   </dataValidations>
@@ -2570,96 +2582,96 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:K16"/>
+  <dimension ref="I1:L16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="8:11">
-      <c r="H1" t="s">
-        <v>278</v>
-      </c>
-      <c r="K1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="2" spans="8:11">
-      <c r="H2" t="s">
-        <v>279</v>
-      </c>
-      <c r="K2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3" spans="8:11">
-      <c r="H3" t="s">
+    <row r="1" spans="9:12">
+      <c r="I1" t="s">
         <v>280</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="8:11">
-      <c r="K4" t="s">
+    <row r="2" spans="9:12">
+      <c r="I2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="5" spans="8:11">
-      <c r="K5" t="s">
+    <row r="3" spans="9:12">
+      <c r="I3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L3" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="6" spans="8:11">
-      <c r="K6" t="s">
+    <row r="4" spans="9:12">
+      <c r="L4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="7" spans="8:11">
-      <c r="K7" t="s">
+    <row r="5" spans="9:12">
+      <c r="L5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="8:11">
-      <c r="K8" t="s">
+    <row r="6" spans="9:12">
+      <c r="L6" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="8:11">
-      <c r="K9" t="s">
+    <row r="7" spans="9:12">
+      <c r="L7" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="8:11">
-      <c r="K10" t="s">
+    <row r="8" spans="9:12">
+      <c r="L8" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="11" spans="8:11">
-      <c r="K11" t="s">
+    <row r="9" spans="9:12">
+      <c r="L9" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="12" spans="8:11">
-      <c r="K12" t="s">
+    <row r="10" spans="9:12">
+      <c r="L10" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="13" spans="8:11">
-      <c r="K13" t="s">
+    <row r="11" spans="9:12">
+      <c r="L11" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="14" spans="8:11">
-      <c r="K14" t="s">
+    <row r="12" spans="9:12">
+      <c r="L12" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="8:11">
-      <c r="K15" t="s">
+    <row r="13" spans="9:12">
+      <c r="L13" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="16" spans="8:11">
-      <c r="K16" t="s">
+    <row r="14" spans="9:12">
+      <c r="L14" t="s">
         <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="9:12">
+      <c r="L15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" spans="9:12">
+      <c r="L16" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000026/metadata_template_ERC000026.xlsx
+++ b/templates/ERC000026/metadata_template_ERC000026.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="gender">'cv_sample'!$I$1:$I$3</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="309">
   <si>
     <t>alias</t>
   </si>
@@ -728,6 +728,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -1485,7 +1488,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -1529,7 +1532,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1559,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2293,6 +2296,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2314,27 +2322,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2354,122 +2362,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -2493,78 +2501,78 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2587,91 +2595,91 @@
   <sheetData>
     <row r="1" spans="9:12">
       <c r="I1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="9:12">
       <c r="I2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="9:12">
       <c r="I3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="9:12">
       <c r="L4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="9:12">
       <c r="L5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="9:12">
       <c r="L6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="9:12">
       <c r="L7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="9:12">
       <c r="L8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="9:12">
       <c r="L9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="9:12">
       <c r="L10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="9:12">
       <c r="L11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="9:12">
       <c r="L12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="9:12">
       <c r="L13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="9:12">
       <c r="L14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="9:12">
       <c r="L15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="9:12">
       <c r="L16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
